--- a/data/baza-tovariv-template.xlsx
+++ b/data/baza-tovariv-template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товари" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Списки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Товари" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Списки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товари'!$A$1:$K$339</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товари'!$A$1:$M$339</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +36,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C2185B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8A8A8A"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,9 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -71,15 +79,6 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="00FFF3CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -150,6 +149,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Цукерня</author>
+  </authors>
+  <commentList>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Заповнює застосунок під час синхронізації. Не редагуйте вручну.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Заповнює застосунок під час синхронізації. Не редагуйте вручну.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Заповнює застосунок під час синхронізації. Не редагуйте вручну.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Заповнює застосунок під час синхронізації. Не редагуйте вручну. За ID застосунок впізнає товар.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -441,20 +470,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -480,7 +511,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Розмір</t>
+          <t>Об’єм / вага</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -503,14 +534,24 @@
           <t>Ціна продажу, грн</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Ціна за 100 г, грн</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Ціна оновлена</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Ціна на цінник, грн</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -940,6 +981,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L14" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -975,6 +1019,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L15" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1010,6 +1057,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L16" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1045,6 +1095,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L17" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1080,6 +1133,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L18" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1120,6 +1176,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L19" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1160,6 +1219,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L20" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1200,6 +1262,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L21" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1240,6 +1305,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L22" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1280,6 +1348,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L23" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1320,6 +1391,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L24" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1360,6 +1434,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L25" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1400,6 +1477,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L26" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1440,6 +1520,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L27" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1480,6 +1563,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L28" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1510,6 +1596,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L29" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1550,6 +1639,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L30" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1590,6 +1682,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L31" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1630,6 +1725,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L32" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1665,6 +1763,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L33" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1706,6 +1807,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L34" t="n">
+        <v>189</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1749,6 +1853,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L35" t="n">
+        <v>35.5</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1790,6 +1897,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L36" t="n">
+        <v>234</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1833,6 +1943,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L37" t="n">
+        <v>47.5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1876,6 +1989,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L38" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1917,32 +2033,31 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="L39" t="n">
+        <v>123.5</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K339"/>
-  <conditionalFormatting sqref="A2:K339">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND($A2&lt;&gt;"",$G2="",$I2="")</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <autoFilter ref="A1:M339"/>
   <dataValidations count="5">
     <dataValidation sqref="B2:B339" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Списки!$A$2:$A$7</formula1>
+      <formula1>=Списки!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C339" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Списки!$B$2:$B$10</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D339" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Списки!$C$2:$C$8</formula1>
+      <formula1>=Списки!$C$2:$C$10</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F339" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Списки!$D$2:$D$3</formula1>
+      <formula1>=Списки!$D$2:$D$10</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G339 H2:H339 I2:I339" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Введіть число" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="G2:G339 H2:H339 I2:I339" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1962,22 +2077,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Група</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Категорія</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Пакування</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Од.</t>
         </is>
@@ -1996,7 +2111,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Стакан</t>
+          <t>Банка</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2018,7 +2133,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Банка</t>
+          <t>ПЕТ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2040,14 +2155,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ПЕТ</t>
+          <t>Скло</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100 г</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Торти</t>
+          <t>Торти і десерти</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2057,41 +2177,51 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Скло</t>
+          <t>Стакан</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>уп</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Інше</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Цукерки</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Коробка</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>пач</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Шоколад</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Цукерки</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Упаковка</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Інше</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Шоколад</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ваговий</t>
+          <t>Пакет</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>кор</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2233,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Штучний</t>
+          <t>Упаковка</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>л</t>
         </is>
       </c>
     </row>
@@ -2113,11 +2248,31 @@
           <t>Печиво</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ваговий</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>порц</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
           <t>Торти</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Штучно</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>набір</t>
         </is>
       </c>
     </row>
